--- a/SLR/Full-Paper-Read/Paper-Review/PS03.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS03.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
@@ -24,9 +24,6 @@
   </si>
   <si>
     <t>The paper proposes the following contributions:</t>
-  </si>
-  <si>
-    <t>The authors discuss the use of Cyber-Physical Systems (CPSs) in large, mobile, and distributed systems like transportation and healthcare, which lead to the development of new cross-CPS applications. These applications enable dynamic, end-to-end scenarios, such as disaster recovery systems. To support this, the authors propose new distributed service composition models that integrate CPS services from different domains to create CPS ecosystems. The paper highlights the advantages of using Cloud-based CPSs, which offer global and rapid access to these services, thereby enhancing the development of CPS ecosystems. However, the dynamic nature of CPS services poses a challenge for service composition. To address this, the authors suggest using models at runtime to create a dynamic middleware framework. This framework facilitates the efficient composition of CPS services by synthesizing software mediators that manage communication between CPS services in the Cloud. The focus of the paper is on supporting the dynamic composition of CPS ecosystems, which can be formed on-demand from existing CPSs, such as spontaneously creating a disaster management system from healthcare and smart transport systems. The authors present basic runtime and mediator models as part of an emergent middleware framework for fast, on-demand service composition in Cloud-based CPSs. Future work will explore the benefits of runtime models in enhancing the safety and reliability of CPS ecosystems.</t>
   </si>
   <si>
     <r>
@@ -36,7 +33,7 @@
         <color theme="1"/>
         <sz val="10.0"/>
       </rPr>
-      <t xml:space="preserve">The authors said: "How to synthesize the composition software? After building the runtime models of two systems, we need synthesis solutions to create a mediator that will implement the composition goals. In particular, it should resolve the differences between the heterogeneous protocol endpoints, and then generate the software that implements this </t>
+      <t xml:space="preserve">The authors investigate quality assurance (QA) challenges in software ecosystems, where different actors collaborate around a shared platform. Using a systematic literature mapping, they found only six relevant papers discussing system architecture, knowledge propagation, test suite understanding, and concerns in mobile and service-oriented architectures. This highlights a significant gap in research. To address this, the authors identify additional QA challenges specific to software ecosystems, such as </t>
     </r>
     <r>
       <rPr>
@@ -46,7 +43,7 @@
         <color theme="1"/>
         <sz val="10.0"/>
       </rPr>
-      <t xml:space="preserve">mediator </t>
+      <t>communication across organizational boundaries</t>
     </r>
     <r>
       <rPr>
@@ -55,15 +52,79 @@
         <color theme="1"/>
         <sz val="10.0"/>
       </rPr>
-      <t>on-the-fly. The generated software will be dynamically deployed between two systems that want to interact. It should be noted that the synthesis process is further supported by ontologies that formalise the domain knowledge."
-2nd reviewer: The authors mention that in their view CPSoS == CPS ecosystems, could be something to keep in mind. Authors also discuss architecture as very central to CPSoS</t>
+      <t xml:space="preserve">, </t>
     </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>user-driven system integration</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>handling unknown execution contexts</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">. They propose a research agenda focusing on these issues throughout the system lifecycle. They also highlight potential benefits of software ecosystems, like </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>improved data feedback from operations</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>, especially in embedded systems. Future work should expand on QA in software ecosystems, explore its impact on ecosystem health, and compare it to other software reuse approaches.</t>
+    </r>
+  </si>
+  <si>
+    <t>Not specifically for CPS, but for embedded systems and mobile applications (i.e., parts of CPS)
+2nd reviewer: They discuss in large what a software ecosystem is, could perhaps be useful for definitions or to cross-check with our paper?
+Could be useful to mention that they found very few papers in their reivew (3 through search + 3 added manually)</t>
   </si>
   <si>
     <t>CPS Case Study / Example availability</t>
   </si>
   <si>
-    <t>Disaster management systems</t>
+    <t>n.a.</t>
+  </si>
+  <si>
+    <t>&lt;add your comment here if any&gt;</t>
   </si>
   <si>
     <t>SECO Tools Availability (add repository or website in the comment)</t>
@@ -72,39 +133,34 @@
     <t>N</t>
   </si>
   <si>
-    <t>&lt;add your comment here if any&gt;</t>
-  </si>
-  <si>
     <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
   </si>
   <si>
     <t>Modeling and Model-Driven Engineering</t>
   </si>
   <si>
-    <t>Continuous software and system engineering</t>
-  </si>
-  <si>
     <t>Requirements engineering</t>
   </si>
   <si>
-    <t>n.a.</t>
-  </si>
-  <si>
-    <t>Manteinability, Interoperabililty, Scalability</t>
+    <t>Testing, architecture (definition), stakeholder engagement, Integration/Interoperability, Adaptability, (Cyber)security (Certification)</t>
   </si>
   <si>
     <t>Does it contribute to answer RQ1?</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Somehow this is also emphasised at runtime, perhaps its own category?</t>
+    <t>Partially</t>
+  </si>
+  <si>
+    <t>Only SECO for embedded and mobile applications.
+2nd reviewer: I like the distinction between architecture at design, and then architecture at runtime (e.g, adaptability), I think this should be somehow clarified in our work eventually</t>
   </si>
   <si>
     <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
   </si>
   <si>
+    <t>Not for CPS, but for general SECO applied to embedded systems and mobile applications</t>
+  </si>
+  <si>
     <t>Does it contribute to answer RQ2?</t>
   </si>
   <si>
@@ -114,19 +170,16 @@
     <t>Application Domain Independent</t>
   </si>
   <si>
-    <t>Emergency Health Care Systems, Emergency Rescue Systems, Emergency Telecommunication Systems, Smart Transportation</t>
-  </si>
-  <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
   </si>
   <si>
-    <t>NOTE: more related to Cyber-Physical System of Systems</t>
-  </si>
-  <si>
     <t>RQ1: In the SECO, what are the main challenges faced during the CPS development?</t>
   </si>
   <si>
     <t>RQ2: How do industry and academia collaborate and benefit in the SECO for CPS development?</t>
+  </si>
+  <si>
+    <t>Note: System literature Mapping</t>
   </si>
   <si>
     <t>Assessment Criterion (Question)</t>
@@ -259,14 +312,14 @@
     </font>
     <font/>
     <font>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Lato"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Lato"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -601,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="60">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -630,11 +683,11 @@
     <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf borderId="16" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="15" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="17" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
@@ -643,7 +696,7 @@
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -655,29 +708,26 @@
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="22" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -707,9 +757,6 @@
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -721,10 +768,10 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="24" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
@@ -733,10 +780,10 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -1051,7 +1098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="261.0" customHeight="1">
+    <row r="3" ht="183.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
@@ -1069,8 +1116,8 @@
       <c r="B4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="17">
-        <v>1.0</v>
+      <c r="C4" s="17" t="s">
+        <v>7</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1078,7 +1125,7 @@
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
       <c r="I4" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -1086,10 +1133,10 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
@@ -1097,47 +1144,47 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="16">
         <v>4.0</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="22" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
+    </row>
+    <row r="7">
       <c r="A7" s="16">
         <v>5.0</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
@@ -1145,7 +1192,7 @@
       <c r="G7" s="25"/>
       <c r="H7" s="18"/>
       <c r="I7" s="23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1153,18 +1200,18 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>16</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="28" t="s">
-        <v>10</v>
+      <c r="I8" s="23" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1172,10 +1219,10 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>9</v>
+        <v>20</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>16</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
@@ -1183,36 +1230,36 @@
       <c r="G9" s="25"/>
       <c r="H9" s="18"/>
       <c r="I9" s="21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="16">
         <v>8.0</v>
       </c>
       <c r="B10" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>24</v>
+      <c r="D10" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1220,11 +1267,11 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="32">
+        <v>23</v>
+      </c>
+      <c r="C11" s="31">
         <f>Quality!C29</f>
-        <v>5.740740741</v>
+        <v>9.259259259</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
@@ -1232,24 +1279,24 @@
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
       <c r="I11" s="21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="B15" s="32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="B17" s="33" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="B16" s="34" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="B17" s="34" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1"/>
@@ -2306,362 +2353,362 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35"/>
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="B2" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="37"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="39"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="40" t="s">
+      <c r="C2" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="42"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="43"/>
+      <c r="B3" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="C3" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="D3" s="36"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="42"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="43"/>
+      <c r="B4" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="42">
+      <c r="C4" s="41">
         <v>1.0</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="43"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="44"/>
-      <c r="B3" s="41" t="s">
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="43"/>
+      <c r="B5" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="42">
+      <c r="C5" s="41">
         <v>1.0</v>
       </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="43"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="44"/>
-      <c r="B4" s="41" t="s">
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="43"/>
+      <c r="B6" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="42">
+      <c r="C6" s="41">
         <v>1.0</v>
       </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="44"/>
-      <c r="B5" s="41" t="s">
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="44"/>
+      <c r="B7" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="45">
-        <v>0.5</v>
-      </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="44"/>
-      <c r="B6" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="42">
+      <c r="C7" s="41">
         <v>1.0</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="46"/>
-      <c r="B7" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="D7" s="47">
+      <c r="D7" s="45">
         <f>COUNTIF(B2:B7,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="45">
         <f>(SUM(C2:C7)/D7)*10</f>
-        <v>9.166666667</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="43"/>
+      <c r="B9" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="C9" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="43"/>
+      <c r="B10" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="44"/>
-      <c r="B9" s="49" t="s">
+      <c r="C10" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="43"/>
+      <c r="B11" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="44"/>
-      <c r="B10" s="49" t="s">
+      <c r="C11" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="43"/>
+      <c r="B12" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="50">
+      <c r="C12" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="43"/>
+      <c r="B13" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="43"/>
+      <c r="B14" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="43"/>
+      <c r="B15" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="43"/>
+      <c r="B16" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="43"/>
+      <c r="B17" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="43"/>
+      <c r="B18" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="44"/>
+      <c r="B19" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="49">
         <v>0.5</v>
       </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="44"/>
-      <c r="B11" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="44"/>
-      <c r="B12" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="44"/>
-      <c r="B13" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="44"/>
-      <c r="B14" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="44"/>
-      <c r="B15" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="44"/>
-      <c r="B16" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="44"/>
-      <c r="B17" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="44"/>
-      <c r="B18" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="46"/>
-      <c r="B19" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="D19" s="47">
+      <c r="D19" s="45">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
         <v>12</v>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="45">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>3.75</v>
+        <v>9.583333333</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="43"/>
+      <c r="B21" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="C21" s="53">
+        <v>0.0</v>
+      </c>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="43"/>
+      <c r="B22" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="44"/>
-      <c r="B21" s="53" t="s">
+      <c r="C22" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="43"/>
+      <c r="B23" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="44"/>
-      <c r="B22" s="53" t="s">
+      <c r="C23" s="52">
+        <v>1.0</v>
+      </c>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="42"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="43"/>
+      <c r="B24" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="55">
+      <c r="C24" s="52">
         <v>1.0</v>
       </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="44"/>
-      <c r="B23" s="53" t="s">
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="42"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="44"/>
+      <c r="B25" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="43"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="44"/>
-      <c r="B24" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="54">
-        <v>0.0</v>
-      </c>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="43"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="46"/>
-      <c r="B25" s="53" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="55">
+      <c r="C25" s="52">
         <v>1.0</v>
       </c>
-      <c r="D25" s="56">
+      <c r="D25" s="54">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E25" s="56">
+      <c r="E25" s="54">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>5</v>
-      </c>
-      <c r="F25" s="43"/>
+        <v>8.333333333</v>
+      </c>
+      <c r="F25" s="42"/>
     </row>
     <row r="26">
-      <c r="A26" s="57" t="s">
+      <c r="A26" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="57">
+        <v>1.0</v>
+      </c>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="42"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="43"/>
+      <c r="B27" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="58" t="s">
+      <c r="C27" s="57">
+        <v>1.0</v>
+      </c>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="42"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="44"/>
+      <c r="B28" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="43"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="44"/>
-      <c r="B27" s="58" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="60">
+      <c r="C28" s="58">
         <v>0.5</v>
       </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="43"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="46"/>
-      <c r="B28" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="59">
-        <v>1.0</v>
-      </c>
-      <c r="D28" s="56">
+      <c r="D28" s="54">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="56">
+      <c r="E28" s="54">
         <f>(SUM(C26:C28)/D28)*10</f>
         <v>8.333333333</v>
       </c>
-      <c r="F28" s="43"/>
+      <c r="F28" s="42"/>
     </row>
     <row r="29">
-      <c r="B29" s="61">
+      <c r="B29" s="59">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="61">
+      <c r="C29" s="59">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>5.740740741</v>
+        <v>9.259259259</v>
       </c>
     </row>
   </sheetData>
